--- a/04-实施战略/03-实施工具/02-A3报告模板.xlsx
+++ b/04-实施战略/03-实施工具/02-A3报告模板.xlsx
@@ -100,7 +100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -127,11 +127,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -155,6 +164,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -538,7 +548,13 @@
           <t>02-A3报告模板</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -546,6 +562,10 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -553,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -644,6 +665,9 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -651,6 +675,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
@@ -658,6 +683,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -665,6 +691,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
@@ -672,6 +699,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
@@ -693,6 +721,9 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -700,6 +731,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
@@ -707,6 +739,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
@@ -714,6 +747,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
@@ -721,6 +755,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
@@ -742,6 +777,9 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -749,6 +787,7 @@
         </is>
       </c>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
@@ -756,6 +795,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
@@ -763,6 +803,7 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
@@ -770,6 +811,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
@@ -791,6 +833,9 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
@@ -798,6 +843,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
@@ -805,6 +851,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
@@ -812,6 +859,7 @@
         </is>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
@@ -819,17 +867,18 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>问题：冷镦工序不良率偏高</t>
+          <t>问题：机加工工序不良率偏高</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Why 1：为什么不良率高？→ 冷镦件尺寸超差多</t>
+          <t>Why 1：为什么不良率高？→ 机加工件尺寸超差多</t>
         </is>
       </c>
     </row>
@@ -868,6 +917,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
@@ -875,6 +925,7 @@
         </is>
       </c>
     </row>
+    <row r="85"/>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
@@ -896,6 +947,9 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -903,6 +957,7 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
@@ -910,6 +965,7 @@
         </is>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
@@ -917,6 +973,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
@@ -924,6 +981,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
@@ -931,6 +989,7 @@
         </is>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
@@ -938,6 +997,7 @@
         </is>
       </c>
     </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
@@ -959,6 +1019,9 @@
         </is>
       </c>
     </row>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
@@ -966,6 +1029,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
@@ -973,6 +1037,7 @@
         </is>
       </c>
     </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
@@ -980,6 +1045,7 @@
         </is>
       </c>
     </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
@@ -987,6 +1053,7 @@
         </is>
       </c>
     </row>
+    <row r="117"/>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
@@ -1022,6 +1089,9 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
@@ -1029,6 +1099,7 @@
         </is>
       </c>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
@@ -1036,6 +1107,7 @@
         </is>
       </c>
     </row>
+    <row r="129"/>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
@@ -1043,6 +1115,7 @@
         </is>
       </c>
     </row>
+    <row r="131"/>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
@@ -1050,6 +1123,7 @@
         </is>
       </c>
     </row>
+    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -1078,6 +1152,9 @@
         </is>
       </c>
     </row>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
@@ -1085,6 +1162,7 @@
         </is>
       </c>
     </row>
+    <row r="142"/>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
@@ -1092,6 +1170,7 @@
         </is>
       </c>
     </row>
+    <row r="144"/>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
@@ -1099,6 +1178,7 @@
         </is>
       </c>
     </row>
+    <row r="146"/>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
@@ -1106,6 +1186,7 @@
         </is>
       </c>
     </row>
+    <row r="148"/>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
@@ -1148,6 +1229,9 @@
         </is>
       </c>
     </row>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
@@ -1155,6 +1239,7 @@
         </is>
       </c>
     </row>
+    <row r="159"/>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
@@ -1190,6 +1275,7 @@
         </is>
       </c>
     </row>
+    <row r="165"/>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
@@ -1197,6 +1283,7 @@
         </is>
       </c>
     </row>
+    <row r="167"/>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
@@ -1456,7 +1543,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>简明扼要描述问题（如"冷镦工序换模时间过长"）</t>
+          <t>简明扼要描述问题（如"机加工工序换模时间过长"）</t>
         </is>
       </c>
     </row>
